--- a/doc/ja/gfarm_monitoring_item_list.xlsx
+++ b/doc/ja/gfarm_monitoring_item_list.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr checkCompatibility="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soda\Documents\prj\etl\gfarm_zabbix\doc\ja\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m-yuuta\Desktop\prj25_01_g-farm\zabbix\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D2F025-C3D5-4E12-942E-09B5F9BFDC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="8475" windowHeight="4725" tabRatio="611"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="611" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート一覧" sheetId="9" r:id="rId1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="146">
   <si>
     <t>警告</t>
     <rPh sb="0" eb="2">
@@ -97,15 +98,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Number of CPUs</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Total memory size</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Free disk space on $1 in %</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -177,10 +170,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>$1 = {$GFMD_PGDATA_DIR}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>gfarm_generic_client_gfhost_sh</t>
   </si>
   <si>
@@ -223,10 +212,6 @@
   </si>
   <si>
     <t>PostgreSQL server is not running</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Low free disk space on {$GFMD_PGDATA_DIR} in %</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -245,10 +230,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Low free disk space on {$GFSD_SPOOL_DIR} in %</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>gfsd warning message in {$GFSD_LOGFILE} on {HOSTNAME}</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -273,18 +254,6 @@
   </si>
   <si>
     <t>Low free memory on server {HOSTNAME}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Processor load is too high on {HOSTNAME}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Zabbix_agentd is not running on {HOSTNAME}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Low free disk space on {$MONITOR_DIR} in %</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -311,15 +280,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>{$MONITOR_DIR}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{$KERNEL_LOGFILE}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Low free disk space on {$GFSD_SPPOL_DIR} in %</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -405,41 +366,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ディレクトリ {$MONITOR_DIR} の属するファイルシステムの空き容量が、{$MONITOR_DIR_FREE_THRESHOLD} パーセントを下回った。</t>
-    <rPh sb="23" eb="24">
-      <t>ゾク</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ヨウリョウ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>シタマワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CPUあたりのシステム平均負荷 (直近1分) が {$LOADAVG_THRESHOLD} を上回った。</t>
-    <rPh sb="11" eb="13">
-      <t>ヘイキン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>チョッキン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>プン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ウワマワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Zabbix サーバと当該ホストの時計が、{$TIME_DIFF_THRESHOLD} 秒より大きくずれている。</t>
     <rPh sb="11" eb="13">
       <t>トウガイ</t>
@@ -456,38 +382,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ディレクトリ {$GFSD_SPOOL_DIR} の属するファイルシステムの空き容量が、{$GFSD_SPOOL_DIR_FREE_THRESHOLD} パーセントを下回った。</t>
-    <rPh sb="26" eb="27">
-      <t>ゾク</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ヨウリョウ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>シタマワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ディレクトリ {$GFMD_PGDATA_DIR} の属するファイルシステムの空き容量が、{$GFMD_PGDATA_DIR_FREE_THRESHOLD} パーセントを下回った。</t>
-    <rPh sb="27" eb="28">
-      <t>ゾク</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ヨウリョウ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>シタマワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ログファイル {$KERNEL_LOGFILE} に、正規表現 "kernel:\s.*I/O\serror" にマッチする行が見つかった。</t>
     <rPh sb="27" eb="31">
       <t>セイキヒョウゲン</t>
@@ -698,26 +592,16 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>{$LOADAVG_THRESHOLD}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{$MEM_FREE_THRESHOLD}</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>{$MONITOR_DIR_FREE_THRESHOLD}</t>
-  </si>
-  <si>
     <t>{$NODATA_TIMEOUT}</t>
   </si>
   <si>
     <t>{$TIME_DIFF_THRESHOLD}</t>
   </si>
   <si>
-    <t>{$ZABBIX_AGENT_TIMEOUT}</t>
-  </si>
-  <si>
     <t>/var/log/messages</t>
   </si>
   <si>
@@ -725,39 +609,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>20</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>30</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>900</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/var/gfarm-spooll</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>{$GFSD_LOGFILE}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{$GFSD_SPOOL_DIR_FREE_THRESHOLD}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{$GFSD_SPOOL_DIR}</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -772,14 +628,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>{$GFMD_PGDATA_DIR_FREE_THRESHOLD}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>{$GFMD_PGDATA_DIR}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>gfmdのログメッセージを記録しているファイルへのパス</t>
     <rPh sb="13" eb="15">
       <t>キロク</t>
@@ -787,23 +635,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>gfmd用に動作させているPostgreSQLのデータ領域へのパス</t>
-    <rPh sb="4" eb="5">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>リョウイキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>/var/gfarm-pgsql</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>gfarm-zabbix トリガー一覧</t>
     <rPh sb="17" eb="19">
       <t>イチラン</t>
@@ -825,22 +656,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>トリガー "Processor load is too high on {HOSTNAME}" を評価する際に参照する、ロードアベレージのしきい値。</t>
-    <rPh sb="49" eb="51">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>チ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>トリガー "Low free memory on server {HOSTNAME}" を評価する際に参照する、空きメモリ率のしきい値。</t>
     <rPh sb="45" eb="47">
       <t>ヒョウカ</t>
@@ -863,50 +678,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>トリガー "Low free disk space on {$GFSD_SPOOL_DIR} in %" を評価する際に参照する、ディスクの空き率のしきい値。</t>
-    <rPh sb="54" eb="56">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>チ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トリガー "Low free disk space on {$GFMD_PGDATA_DIR} in %" を評価する際に参照する、ディスクの空き率のしきい値。</t>
-    <rPh sb="55" eb="57">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>チ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ファイルシステムノードとして、メタデータサーバに登録されたホスト名。</t>
     <rPh sb="24" eb="26">
       <t>トウロク</t>
@@ -919,48 +690,6 @@
   <si>
     <t>-
 ('hostname -f' の出力結果を用いる)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トリガー "Low free disk space on {$MONITOR_DIR} in %" を評価する際に参照する、ファイルシステムの空き率のしきい値。</t>
-    <rPh sb="51" eb="53">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>チ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トリガー "Low free disk space on {$MONITOR_DIR} in %" を評価する際に、ファイルシステムの空き率チェックの対象とするディレクトリへのパス。</t>
-    <rPh sb="67" eb="68">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="69" eb="70">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>タイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>gfsd のスプール領域へのパス。</t>
-    <rPh sb="10" eb="12">
-      <t>リョウイキ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1029,109 +758,12 @@
     <t>Template_Gfarm_gfsd</t>
   </si>
   <si>
-    <t>Template_Gfarm_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Template_Gfarm_gfsd_linux_alt</t>
-  </si>
-  <si>
-    <t>Template_Gfarm_gfmd_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Template_Gfarm_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Template_Gfarm_linux</t>
   </si>
   <si>
     <t>Linux用</t>
     <rPh sb="5" eb="6">
       <t>ヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>末尾が "_alt" となっているテンプレートは、Template OS Linux を利用しない場合のみ使用する。</t>
-    <rPh sb="0" eb="2">
-      <t>マツビ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Temlate OS Linux を使わない場合の gfsd用追加監視項目</t>
-    <rPh sb="18" eb="19">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カンシ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Temlate OS Linux を使わない場合の gfｍd用追加監視項目</t>
-    <rPh sb="18" eb="19">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>カンシ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Temlate OS Linux を使わない場合の Linux用追加監視項目</t>
-    <rPh sb="18" eb="19">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>カンシ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>コウモク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1230,10 +862,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Template_Gfarm_gfsd_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>トリガー "Time drift between Zabbix server and {HOSTNAME}" のしきい値。Zabbix サーバと監視対象ホストの間で、時計のずれが当該時間より大きければ、アラートを上げる。</t>
     <rPh sb="59" eb="60">
       <t>チ</t>
@@ -1262,30 +890,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>トリガー "Zabbix_agentd is not running on {HOSTNAME}" において、当該期間 zabbix-agentd から反応がない場合、アラートを上げる。</t>
-    <rPh sb="55" eb="59">
-      <t>トウガイキカン</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ハンノウ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="89" eb="90">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Template_Gfarm_gfmd_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Template_Gfarm_gfsd_linux_alt</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Available memory size</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1310,25 +914,6 @@
   </si>
   <si>
     <t>Time drift between Zabbix server and {HOSTNAME}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CPU(s) load</t>
-  </si>
-  <si>
-    <t>$1 = {$MONITOR_DIR}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Number of running processes $1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>$1 = {$GFSD_SPOOL_DIR}</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>$1 = zabbix_agentd</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1405,19 +990,6 @@
   </si>
   <si>
     <t>Template_Gfarm_represent_client</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>zabbxi-agentd から {$ZABBIX_AGENT_TIMEOUT} 秒以上、応答がない。</t>
-    <rPh sb="41" eb="42">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>オウトウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1520,7 +1092,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1634,18 +1206,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1654,10 +1226,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1671,9 +1239,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1681,12 +1246,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1713,25 +1272,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1763,9 +1313,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1803,9 +1353,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1840,7 +1390,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1875,7 +1425,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2048,98 +1598,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr applyStyles="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="49.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="22" t="s">
+    <row r="1" spans="1:2" ht="27.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2151,261 +1672,149 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr applyStyles="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.3984375" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:4" ht="27.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="D4" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="22" t="s">
+      <c r="D7" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="36" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="36" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="36" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A10" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.15">
-      <c r="A11" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="D9" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="36" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A14" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A15" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="D11" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="24" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="29" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2417,431 +1826,431 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr applyStyles="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="50.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" customWidth="1"/>
+    <col min="4" max="4" width="5.59765625" customWidth="1"/>
+    <col min="5" max="5" width="30.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.8984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.15">
-      <c r="A3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>19</v>
+      <c r="C3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
         <v>300</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
         <v>300</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3">
         <v>3600</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
         <v>600</v>
       </c>
-      <c r="E7" s="34" t="s">
-        <v>174</v>
+      <c r="E7" s="26" t="s">
+        <v>123</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>174</v>
+      <c r="E8" s="26" t="s">
+        <v>123</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11">
         <v>3600</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="E9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11">
+        <v>300</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="11">
+        <v>600</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A10" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13">
-        <v>300</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="D12" s="11">
         <v>600</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="13">
-        <v>600</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="F12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
         <v>300</v>
       </c>
-      <c r="E13" s="31" t="s">
-        <v>28</v>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="31" t="s">
-        <v>29</v>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="31" t="s">
-        <v>29</v>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11">
         <v>3600</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="E16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13">
-        <v>3600</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="10" t="s">
+      <c r="C18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="11">
+        <v>600</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="11">
         <v>600</v>
       </c>
-      <c r="E18" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="13">
+      <c r="E19" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="11">
         <v>600</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="13">
-        <v>600</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>167</v>
+      <c r="E20" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>121</v>
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
         <v>300</v>
       </c>
-      <c r="E21" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>168</v>
+      <c r="E21" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>122</v>
       </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>50</v>
+      <c r="E22" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
@@ -2850,17 +2259,17 @@
       <c r="D23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23" s="33" t="s">
-        <v>50</v>
+      <c r="E23" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>6</v>
@@ -2869,17 +2278,17 @@
       <c r="D24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>50</v>
+      <c r="E24" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>7</v>
@@ -2888,154 +2297,32 @@
       <c r="D25" s="3">
         <v>300</v>
       </c>
-      <c r="E25" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>50</v>
+      <c r="E25" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>50</v>
+      <c r="E26" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="13">
-        <v>3600</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="3">
-        <v>3600</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A29" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D29" s="8">
-        <v>300</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A30" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8">
-        <v>300</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8">
-        <v>300</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="8"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A32" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="8">
-        <v>3600</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3046,501 +2333,421 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr applyStyles="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-    <col min="2" max="2" width="53.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="53.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8984375" customWidth="1"/>
     <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="43.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.15">
-      <c r="A3" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="24" t="s">
+    <row r="1" spans="1:6" ht="27.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" ht="24" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" ht="36" x14ac:dyDescent="0.15">
-      <c r="A10" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="16" t="s">
+    <row r="10" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A11" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A12" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="21" t="s">
+      <c r="D11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A13" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="20" t="s">
+      <c r="D12" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="21" t="s">
+      <c r="D13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:6" ht="36" x14ac:dyDescent="0.15">
-      <c r="A15" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="C15" s="21" t="s">
+      <c r="D14" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+      <c r="A15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A16" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="21" t="s">
+      <c r="D15" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A16" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" ht="24" x14ac:dyDescent="0.15">
+      <c r="D16" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" ht="24" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="25"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" ht="48" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A20" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="33"/>
+        <v>65</v>
+      </c>
+      <c r="E26" s="25"/>
       <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" ht="36" x14ac:dyDescent="0.15">
-      <c r="A27" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6" ht="36" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-    </row>
-    <row r="29" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A29" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A30" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" ht="24" x14ac:dyDescent="0.15">
-      <c r="A31" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E31" s="10"/>
-      <c r="F31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
